--- a/documentation/booksy_plan_isporuke.xlsx
+++ b/documentation/booksy_plan_isporuke.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hrvoje\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hrvoje\Documents\GitHub\OICAR\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92D03B7-6555-441B-8801-6B1E2CD7F3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66321A90-8F21-489F-A9E0-336DF773B7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -665,84 +665,84 @@
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1021,593 +1021,568 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="14" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="14" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="14" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="14" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="14" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="16" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="16" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+    </row>
+    <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+    </row>
+    <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+    </row>
+    <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+    </row>
+    <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="21" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="23" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="25" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="26" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="20"/>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="31" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="34" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="36" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="21" t="s">
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+    </row>
+    <row r="37" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" s="19" t="s">
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="38" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="19" t="s">
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="G34:G39"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="G28:G33"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="G22:G27"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="G16:G21"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="F10:F15"/>
-    <mergeCell ref="G10:G15"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:A9"/>
@@ -1615,6 +1590,31 @@
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="G4:G9"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="G10:G15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="G16:G21"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="G22:G27"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="C28:C33"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="G28:G33"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="C34:C39"/>
+    <mergeCell ref="F34:F39"/>
+    <mergeCell ref="G34:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1630,380 +1630,380 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="11" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
+      <c r="A5" s="12"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="11" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="13" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="13" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="11" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
+      <c r="A17" s="12"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="11" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="13" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="13" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="13" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="13" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="13" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="13" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
+      <c r="A29" s="12"/>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="11" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="11" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="13" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="13" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="12" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="24"/>
+      <c r="A41" s="12"/>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="11" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="13" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="25" t="s">
+      <c r="A48" s="13" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="13" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="13" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="13" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24" t="s">
+      <c r="A52" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="24"/>
+      <c r="A53" s="12"/>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="11" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="13" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="25" t="s">
+      <c r="A57" s="13" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="25" t="s">
+      <c r="A58" s="13" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="25" t="s">
+      <c r="A59" s="13" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="24" t="s">
+      <c r="A60" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="13" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="25" t="s">
+      <c r="A62" s="13" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="11" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="25" t="s">
+      <c r="A64" s="13" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="25" t="s">
+      <c r="A65" s="13" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="24" t="s">
+      <c r="A66" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="24"/>
+      <c r="A67" s="12"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="11" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="25" t="s">
+      <c r="A69" s="13" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="25" t="s">
+      <c r="A70" s="13" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="25" t="s">
+      <c r="A71" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="25" t="s">
+      <c r="A72" s="13" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="25" t="s">
+      <c r="A73" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="25" t="s">
+      <c r="A75" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="25" t="s">
+      <c r="A76" s="13" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="24" t="s">
+      <c r="A78" s="12" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2024,64 +2024,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="1" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="6" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="8" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="6" t="s">
         <v>150</v>
       </c>
     </row>

--- a/documentation/booksy_plan_isporuke.xlsx
+++ b/documentation/booksy_plan_isporuke.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hrvoje\Documents\GitHub\OICAR\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hrvoje\Documents\GitHub\Tomo\OICAR\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66321A90-8F21-489F-A9E0-336DF773B7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B95308-A57F-4A0C-9503-9A1B8032338E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -567,7 +567,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -622,6 +622,30 @@
         <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF99"/>
+        <bgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF99"/>
+        <bgColor rgb="FFD1EDE6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF99"/>
+        <bgColor rgb="FFF1EFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF1EFE8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -663,23 +687,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -710,38 +722,68 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -817,6 +859,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FF66FF99"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1021,26 +1066,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1066,523 +1111,548 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="20"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="2" t="s">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="2" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="2" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="2" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="2" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="21"/>
+    </row>
+    <row r="12" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="21"/>
+    </row>
+    <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="26"/>
+      <c r="G13" s="21"/>
+    </row>
+    <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="21"/>
+    </row>
+    <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="26"/>
+      <c r="G15" s="21"/>
+    </row>
+    <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+    </row>
+    <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+    </row>
+    <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+    </row>
+    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+    </row>
+    <row r="21" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="23" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+    </row>
+    <row r="24" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+    </row>
+    <row r="25" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+    </row>
+    <row r="26" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+    </row>
+    <row r="30" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="35" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-    </row>
-    <row r="12" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+    </row>
+    <row r="37" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+    </row>
+    <row r="38" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+    </row>
+    <row r="39" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-    </row>
-    <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="17" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-    </row>
-    <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-    </row>
-    <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-    </row>
-    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-    </row>
-    <row r="21" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="24" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="26" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-    </row>
-    <row r="27" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-    </row>
-    <row r="28" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-    </row>
-    <row r="30" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-    </row>
-    <row r="31" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-    </row>
-    <row r="32" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-    </row>
-    <row r="33" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="16"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-    </row>
-    <row r="34" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="20"/>
-    </row>
-    <row r="35" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="16"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-    </row>
-    <row r="36" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-    </row>
-    <row r="37" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-    </row>
-    <row r="38" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-    </row>
-    <row r="39" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="16"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="C34:C39"/>
+    <mergeCell ref="F34:F39"/>
+    <mergeCell ref="G34:G39"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="C28:C33"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="G28:G33"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="G22:G27"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="G16:G21"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="G10:G15"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:A9"/>
@@ -1590,31 +1660,6 @@
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="G4:G9"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="F10:F15"/>
-    <mergeCell ref="G10:G15"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="G16:G21"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="G22:G27"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="G28:G33"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="G34:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1630,380 +1675,380 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
+      <c r="A5" s="8"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="9" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="9" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="9" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
+      <c r="A17" s="8"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="7" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="9" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="9" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="7" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="9" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="9" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="12"/>
+      <c r="A29" s="8"/>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="7" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="9" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="7" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="9" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="8" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
+      <c r="A41" s="8"/>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="7" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="9" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="9" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="9" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="9" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="9" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="12"/>
+      <c r="A53" s="8"/>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="8" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="9" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="9" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
+      <c r="A67" s="8"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="9" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="9" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="9" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="9" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="12" t="s">
+      <c r="A78" s="8" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2024,11 +2069,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2042,46 +2087,46 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="2" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>150</v>
       </c>
     </row>
